--- a/安全体检报告/风险清单/安全事件清单.xlsx
+++ b/安全体检报告/风险清单/安全事件清单.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S55"/>
+  <dimension ref="A1:S86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.2788461538462" customWidth="1" min="1" max="1"/>
@@ -584,8 +584,7 @@
     <col width="19.7019230769231" customWidth="1" min="11" max="11"/>
     <col width="19.5480769230769" customWidth="1" min="12" max="12"/>
     <col width="26.7596153846154" customWidth="1" min="13" max="13"/>
-    <col width="16.3365384615385" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="14" max="15"/>
     <col width="26" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="20"/>
@@ -693,7 +692,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>incident-5ae93b35-5696-4be1-9848-46e5e19b90b1</t>
+          <t>incident-e8a1af25-06f9-4e5d-aad3-79e401e0c7da</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -703,12 +702,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>病毒木马活动</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -716,14 +715,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -742,32 +741,32 @@
         </is>
       </c>
       <c r="K2" s="6" t="n">
-        <v>46196.65336805556</v>
+        <v>46213.81315972222</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>46198.41525462963</v>
+        <v>46213.81271990741</v>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>119.242.210.12</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="inlineStr">
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -786,7 +785,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>incident-21a53163-ac61-4007-b7a2-2cf57d986f83</t>
+          <t>incident-f9f03bda-e8f9-4b25-9489-31f31abae541</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -796,12 +795,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>主机失陷活动</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -809,14 +808,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>处置完成</t>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -835,32 +834,32 @@
         </is>
       </c>
       <c r="K3" s="6" t="n">
-        <v>46196.65336805556</v>
+        <v>46213.81379629629</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>46198.41525462963</v>
+        <v>46213.81341435185</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>92.78.41.143</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr">
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -870,14 +869,16 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S3" s="6" t="n">
-        <v>46211.72042824074</v>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>incident-398a71df-03ef-41de-a5be-8744cc1110c8</t>
+          <t>incident-71ac4e22-daea-4105-a1da-ab97631a4390</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -887,12 +888,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>病毒木马活动</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -900,14 +901,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -926,32 +927,32 @@
         </is>
       </c>
       <c r="K4" s="6" t="n">
-        <v>46196.65336805556</v>
+        <v>46213.86122685186</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>46198.41524305556</v>
+        <v>46213.86081018519</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>227.161.123.227</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="inlineStr">
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -970,7 +971,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>incident-0c86f790-4469-46db-b1a6-8254e239ea5b</t>
+          <t>incident-5b352a72-af84-4d32-b70c-2ef2b6610af8</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -980,12 +981,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>主机失陷活动</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -993,19 +994,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>后门攻击事件</t>
+          <t>漏洞利用</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -1019,32 +1020,32 @@
         </is>
       </c>
       <c r="K5" s="6" t="n">
-        <v>46196.65336805556</v>
+        <v>46213.04708333333</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>46198.41524305556</v>
+        <v>46213.88939814815</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>129.37.235.168</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr">
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -1063,7 +1064,7 @@
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>incident-c81b37fe-80ba-45c6-9cce-536511a4909d</t>
+          <t>incident-785f8c89-6587-450b-bcbc-a468988c9137</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1073,12 +1074,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1086,14 +1087,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1112,32 +1113,32 @@
         </is>
       </c>
       <c r="K6" s="6" t="n">
-        <v>46196.65336805556</v>
+        <v>46213.89001157408</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>46198.41524305556</v>
+        <v>46213.88962962963</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>115.95.216.179</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -1156,7 +1157,7 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>incident-459399db-fae5-483d-8019-8042d45feece</t>
+          <t>incident-d45fae82-ac6f-412f-8876-dacf93391316</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1166,12 +1167,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>172.25.115.179</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1179,14 +1180,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1205,32 +1206,32 @@
         </is>
       </c>
       <c r="K7" s="6" t="n">
-        <v>46196.65336805556</v>
+        <v>46216.631875</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>46198.41524305556</v>
+        <v>46216.63142361111</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>8.8.8.8</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
+          <t>172.25.115.179</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -1249,7 +1250,7 @@
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>incident-464bc739-6c3d-4b57-b2dc-c1f63e72b4d0</t>
+          <t>incident-95b05250-25c5-4369-810d-a0d6adc74ccc</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1259,12 +1260,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>192.168.145.217</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1272,14 +1273,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1298,32 +1299,32 @@
         </is>
       </c>
       <c r="K8" s="6" t="n">
-        <v>46196.65336805556</v>
+        <v>46216.631875</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>46198.41524305556</v>
+        <v>46216.63142361111</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>223.5.5.5</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr">
+          <t>192.168.145.217</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -1342,7 +1343,7 @@
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>incident-fd133e4e-a4dd-4b97-8ac5-0c4583c7d20e</t>
+          <t>incident-2b90aa47-6511-49bf-a903-3b9d58e37db7</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1352,12 +1353,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1365,14 +1366,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1391,32 +1392,32 @@
         </is>
       </c>
       <c r="K9" s="6" t="n">
-        <v>46196.65336805556</v>
+        <v>46216.62233796297</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>46198.41524305556</v>
+        <v>46216.621875</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>73.200.39.49</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr">
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>210.232.81.231</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -1435,7 +1436,7 @@
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>incident-cb2cc9cc-6c0a-4c60-80ed-fa73acb6b5da</t>
+          <t>incident-038c0a2d-8510-4d20-bba2-5caf25ee1fb1</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1445,12 +1446,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>172.16.53.167</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1458,14 +1459,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -1484,32 +1485,32 @@
         </is>
       </c>
       <c r="K10" s="6" t="n">
-        <v>46196.65336805556</v>
+        <v>46216.62353009259</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>46198.41524305556</v>
+        <v>46216.62309027778</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>8.8.8.8</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
+          <t>172.16.53.167</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -1528,7 +1529,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>incident-2ac3b644-d9d2-4ebb-abf6-c2f01c4cac58</t>
+          <t>incident-85dde02f-b060-4bef-9909-b27a15546c67</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1538,12 +1539,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>10.69.92.35</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1551,14 +1552,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -1577,32 +1578,32 @@
         </is>
       </c>
       <c r="K11" s="6" t="n">
-        <v>46196.65336805556</v>
+        <v>46216.62353009259</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>46198.41524305556</v>
+        <v>46216.62309027778</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>223.5.5.5</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="inlineStr">
+          <t>10.69.92.35</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -1621,88 +1622,88 @@
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>incident-010a7275-2a8b-49dd-8b37-acd4aa516b26</t>
+          <t>incident-eb7b44c8-8bab-4dd8-9f8f-d74755a1b50f</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>已生成事件告警更新源ip668</t>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>192.168.26.44</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>勒索攻击</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>处置完成</t>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>弱口令</t>
+          <t>后门攻击事件</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Web弱口令</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>失败</t>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
         </is>
       </c>
       <c r="K12" s="6" t="n">
-        <v>46208.45471064815</v>
+        <v>46216.62859953703</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>46216.8025462963</v>
+        <v>46216.628125</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>200.200.42.199</t>
+          <t>66.148.35.122</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>192.168.26.44</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="inlineStr">
-        <is>
-          <t>200.200.42.200,200.200.42.199</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr">
-        <is>
-          <t>STA (1234)</t>
-        </is>
-      </c>
-      <c r="R12" s="20" t="inlineStr">
-        <is>
-          <t>已推送</t>
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>210.232.81.231</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R12" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -1714,7 +1715,7 @@
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>incident-87931dc3-2b8d-4877-89d9-2996c6957ec4</t>
+          <t>incident-bf25fd1e-7b61-4747-9de9-d909fe12f584</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1724,12 +1725,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>10.212.64.231</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1737,14 +1738,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>已忽略</t>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1763,32 +1764,32 @@
         </is>
       </c>
       <c r="K13" s="6" t="n">
-        <v>46196.65336805556</v>
+        <v>46216.63965277778</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>46198.41524305556</v>
+        <v>46216.63917824074</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>223.5.5.5</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="inlineStr">
+          <t>10.212.64.231</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -1798,14 +1799,16 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S13" s="6" t="n">
-        <v>46198.41525462963</v>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>incident-00df5f64-672f-4b2d-8692-aecf7e668ca7</t>
+          <t>incident-f027229d-40fb-4b48-a481-5d60f2fe2c93</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1815,10 +1818,10 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>192.168.181.75</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+          <t>10.132.61.134</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>疑似攻击行为</t>
         </is>
@@ -1833,9 +1836,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
-        <is>
-          <t>已忽略</t>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1854,32 +1857,32 @@
         </is>
       </c>
       <c r="K14" s="6" t="n">
-        <v>46217.68916666666</v>
+        <v>46216.63964120371</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>46217.69076388889</v>
+        <v>46216.63917824074</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.8.8.8</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>192.168.181.75</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="inlineStr">
-        <is>
-          <t>162.70.245.232</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="inlineStr">
+          <t>10.132.61.134</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -1898,7 +1901,7 @@
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>incident-8ab6099b-3c7d-422b-bb8f-4f69521568b0</t>
+          <t>incident-efcf671e-74a4-44ba-b3d0-d089881734f4</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1908,10 +1911,10 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>25.130.60.101</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+          <t>10.116.228.67</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>疑似攻击行为</t>
         </is>
@@ -1926,9 +1929,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>已忽略</t>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1947,32 +1950,32 @@
         </is>
       </c>
       <c r="K15" s="6" t="n">
-        <v>46217.41965277777</v>
+        <v>46216.64098379629</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>46217.42125</v>
+        <v>46216.64050925926</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>116.97.138.115</t>
+          <t>223.5.5.5</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>25.130.60.101</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="inlineStr">
-        <is>
-          <t>116.97.138.115</t>
-        </is>
-      </c>
-      <c r="Q15" s="5" t="inlineStr">
+          <t>10.116.228.67</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -1991,7 +1994,7 @@
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>incident-b0623890-0c2a-47f3-9c5d-2a1a6f19d5b1</t>
+          <t>incident-336bab6f-c88a-4a06-a75d-bc64b6206474</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2001,10 +2004,10 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>192.168.218.171</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
+          <t>172.18.224.166</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>疑似攻击行为</t>
         </is>
@@ -2019,9 +2022,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>已忽略</t>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2040,32 +2043,32 @@
         </is>
       </c>
       <c r="K16" s="6" t="n">
-        <v>46217.69652777778</v>
+        <v>46216.64098379629</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>46217.69811342593</v>
+        <v>46216.64050925926</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.8.8.8</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>192.168.218.171</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>211.202.146.41</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
+          <t>172.18.224.166</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -2084,22 +2087,22 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>incident-c5e7bccd-0c65-495c-8c90-bcc900a53575</t>
+          <t>incident-26e99b4a-5191-40b5-85e3-04fd49ac8cf0</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>主机存在Apache Log4j2远程代码执行漏洞(CVE-2021-45046/CVE-2021-44228)</t>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>10.227.11.12</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>192.168.182.53</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2107,60 +2110,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>漏洞利用</t>
+          <t>后门攻击事件</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Web框架漏洞</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>失败</t>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
         </is>
       </c>
       <c r="K17" s="6" t="n">
-        <v>46198.44909722222</v>
+        <v>46216.70746527778</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>46218.69664351852</v>
+        <v>46216.70700231481</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>192.168.101.97</t>
+          <t>8.8.8.8</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>11.11.156.101,11.11.19.101</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>STA (B501C49C),STA (D1DE0506)</t>
+          <t>192.168.182.53</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
         </is>
       </c>
       <c r="R17" s="22" t="inlineStr">
@@ -2177,22 +2180,22 @@
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>incident-a60f4da8-e861-4fd3-930f-66461bdf4d74</t>
+          <t>incident-23b56028-448f-4146-91ca-f70a9bb9f6ee</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>主机存在Apache Log4j2远程代码执行漏洞(CVE-2021-45046/CVE-2021-44228)</t>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>192.168.101.97</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>192.168.163.223</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2200,60 +2203,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>漏洞利用</t>
+          <t>后门攻击事件</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Web框架漏洞</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>失败</t>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
         </is>
       </c>
       <c r="K18" s="6" t="n">
-        <v>46198.44909722222</v>
+        <v>46216.70746527778</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>46219.63732638889</v>
+        <v>46216.70700231481</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>192.168.101.97</t>
+          <t>223.5.5.5</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>11.11.156.101,11.11.19.101</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>STA (B501C49C),STA (D1DE0506)</t>
+          <t>192.168.163.223</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
         </is>
       </c>
       <c r="R18" s="22" t="inlineStr">
@@ -2270,7 +2273,7 @@
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>incident-66293780-cfe8-473d-8602-0a514c4231cf</t>
+          <t>incident-3c2fa4f3-677d-4870-8567-ebd0b2c69b50</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2280,17 +2283,17 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>192.168.15.38</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
@@ -2298,9 +2301,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>处置中</t>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -2319,32 +2322,32 @@
         </is>
       </c>
       <c r="K19" s="6" t="n">
-        <v>46217.66635416666</v>
+        <v>46216.71653935185</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>46217.66795138889</v>
+        <v>46216.71608796297</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>144.245.22.166</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>192.168.15.38</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="inlineStr">
-        <is>
-          <t>65.19.64.41</t>
-        </is>
-      </c>
-      <c r="Q19" s="5" t="inlineStr">
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>210.232.81.231</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -2363,7 +2366,7 @@
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>incident-d9f60199-ffbe-4a70-956a-2e5de81aa1fb</t>
+          <t>incident-14de7387-1930-4b01-aba7-db0fdbb582a4</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2373,10 +2376,10 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>10.158.63.131</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+          <t>172.28.129.245</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>疑似攻击行为</t>
         </is>
@@ -2391,9 +2394,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>已忽略</t>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2412,32 +2415,32 @@
         </is>
       </c>
       <c r="K20" s="6" t="n">
-        <v>46217.71190972222</v>
+        <v>46216.73271990741</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>46217.71350694444</v>
+        <v>46216.7322337963</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>236.193.146.12</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10.158.63.131</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>188.122.177.110</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="inlineStr">
+          <t>172.28.129.245</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -2456,88 +2459,88 @@
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>incident-0799c145-56f2-49cb-adbd-1888d4b21a73</t>
+          <t>incident-287f14de-9f63-4714-8d8f-135a08026c5e</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>数据工厂模板：通过工具窃取密码等异常行为</t>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>168.196.23.21</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
+          <t>46.46.231.127</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>勒索攻击</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>处置完成</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>后门攻击事件</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
-        <is>
-          <t>尝试</t>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
         </is>
       </c>
       <c r="K21" s="6" t="n">
-        <v>46216.48506944445</v>
+        <v>46216.84</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>46216.8025462963</v>
+        <v>46216.83952546296</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>232.82.254.233</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P21" s="5" t="inlineStr">
-        <is>
-          <t>46.34.63.17,46.34.63.44,46.34.63.53,46.34.63.7,46.34.63.3,46.34.63.31,46.34.63.78,46.34.63.6,46.34.63.54,46.34.63.69,46.34.63.100,46.34.63.63,46.34.63.72,46.34.63.8,46.34.63.96,46.34.63.65,46.34.63.47,46.34.63.70,46.34.63.83,46.34.63.61,46.34.63.22,46.34.63.36,46.34.63.93,46.34.63.11,46.34.63.99,46.34.63.60,46.34.63.62,46.34.63.23,46.34.63.37,46.34.63.76,46.34.63.20,46.34.63.28,46.34.63.98,46.34.63.87,46.34.63.14,46.34.63.42,46.34.63.101,46.34.63.71,46.34.63.85,46.34.63.1,46.34.63.33,46.34.63.19,46.34.63.12,46.34.63.25,46.34.63.18,46.34.63.92,46.34.63.2,46.34.63.29,46.34.63.59,46.34.63.75,46.34.63.10,46.34.63.35,46.34.63.66,46.34.63.86,46.34.63.91,46.34.63.51,46.34.63.58,46.34.63.4,46.34.63.5,46.34.63.95,46.34.63.84,46.34.63.9,46.34.63.39,46.34.63.40,46.34.63.38,46.34.63.41,46.34.63.90,46.34.63.73,46.34.63.50,46.34.63.94,46.34.63.74,46.34.63.77,46.34.63.82,46.34.63.80,46.34.63.64,46.34.63.52,46.34.63.49,46.34.63.16,46.34.63.97,46.34.63.24,46.34.63.67,46.34.63.55,46.34.63.48,46.34.63.13,46.34.63.46,46.34.63.88,46.34.63.30,46.34.63.34,46.34.63.68,46.34.63.15,46.34.63.32,46.34.63.21,46.34.63.56,46.34.63.26,46.34.63.27,46.34.63.57,46.34.63.79,46.34.63.43,46.34.63.89,46.34.63.81</t>
-        </is>
-      </c>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R21" s="20" t="inlineStr">
-        <is>
-          <t>已推送</t>
+          <t>46.46.231.127</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R21" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -2549,7 +2552,7 @@
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>incident-12185bc2-b2ec-4679-b1ee-be95bfe45d16</t>
+          <t>incident-db7459ac-a96e-4a5b-8bda-b1f8e3fbaf0b</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2559,17 +2562,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>172.23.105.11</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>疑似攻击行为</t>
+          <t>172.23.52.205</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>真实攻击成功</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>银狐病毒</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -2577,9 +2580,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>已忽略</t>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>待处置</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2598,32 +2601,32 @@
         </is>
       </c>
       <c r="K22" s="6" t="n">
-        <v>46217.43493055556</v>
+        <v>46217.74184027778</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>46217.43646990741</v>
+        <v>46217.74133101852</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>65.151.230.99</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>172.23.105.11</t>
-        </is>
-      </c>
-      <c r="P22" s="5" t="inlineStr">
-        <is>
-          <t>65.151.230.99</t>
-        </is>
-      </c>
-      <c r="Q22" s="5" t="inlineStr">
+          <t>172.23.52.205</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>47.104.32.13</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -2642,7 +2645,7 @@
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>incident-280b4843-f628-4648-9756-025a7a853d9a</t>
+          <t>incident-54cbb13a-c47e-4e63-a465-1ab42274231b</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2652,17 +2655,17 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>91.143.180.251</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
@@ -2670,9 +2673,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -2691,32 +2694,32 @@
         </is>
       </c>
       <c r="K23" s="6" t="n">
-        <v>46217.43166666666</v>
+        <v>46216.71672453704</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>46217.43322916667</v>
+        <v>46216.71626157407</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>38.126.180.153</t>
+          <t>175.198.194.151</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>91.143.180.251</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>38.126.180.153</t>
-        </is>
-      </c>
-      <c r="Q23" s="5" t="inlineStr">
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>210.232.81.231</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -2726,16 +2729,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S23" s="6" t="n">
+        <v>46216.716875</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>incident-636eb5b9-7143-4ddd-9663-46914e514cc7</t>
+          <t>incident-c245a908-5b7d-406b-b1d1-93547286386f</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2745,17 +2746,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>172.21.153.184</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>疑似攻击行为</t>
+          <t>192.168.97.185</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>真实攻击成功</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>银狐病毒</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
@@ -2763,9 +2764,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G24" s="15" t="inlineStr">
-        <is>
-          <t>已忽略</t>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -2784,32 +2785,32 @@
         </is>
       </c>
       <c r="K24" s="6" t="n">
-        <v>46217.39888888889</v>
+        <v>46216.49746527777</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>46217.40047453704</v>
+        <v>46216.49699074074</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>183.131.251.28</t>
+          <t>224.206.116.164</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>172.21.153.184</t>
-        </is>
-      </c>
-      <c r="P24" s="5" t="inlineStr">
-        <is>
-          <t>183.131.251.28</t>
-        </is>
-      </c>
-      <c r="Q24" s="5" t="inlineStr">
+          <t>192.168.97.185</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -2819,109 +2820,105 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S24" s="6" t="n">
+        <v>46216.49795138889</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>incident-b9ef3f7f-4c92-49e3-aa1b-2b652afc442d</t>
+          <t>incident-8bb741d2-168e-411f-a7e3-558633356c5d</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>数据工厂模板：通过工具窃取密码等异常行为</t>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>168.196.23.21</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
+          <t>172.17.215.206</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>勒索攻击</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>处置完成</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>后门攻击事件</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="19" t="inlineStr">
-        <is>
-          <t>尝试</t>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
         </is>
       </c>
       <c r="K25" s="6" t="n">
-        <v>46216.59666666666</v>
+        <v>46217.71337962963</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>46216.8025462963</v>
+        <v>46217.71292824074</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.1.1.1</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="inlineStr">
-        <is>
-          <t>46.34.63.46,46.34.63.88,46.34.63.17,46.34.63.39,46.34.63.41,46.34.63.4,46.34.63.71,46.34.63.18,46.34.63.61,46.34.63.28,46.34.63.51,46.34.63.75,46.34.63.42,46.34.63.10,46.34.63.27,46.34.63.100,46.34.63.35,46.34.63.62,46.34.63.38,46.34.63.24,46.34.63.63,46.34.63.72,46.34.63.82,46.34.63.7,46.34.63.80,46.34.63.36,46.34.63.54,46.34.63.77,46.34.63.55,46.34.63.25,46.34.63.47,46.34.63.90,46.34.63.32,46.34.63.52,46.34.63.11,46.34.63.68,46.34.63.49,46.34.63.85,46.34.63.78,46.34.63.95,46.34.63.67,46.34.63.94,46.34.63.6,46.34.63.8,46.34.63.66,46.34.63.99,46.34.63.20,46.34.63.33,46.34.63.22,46.34.63.34,46.34.63.101,46.34.63.97,46.34.63.59,46.34.63.5,46.34.63.1,46.34.63.56,46.34.63.12,46.34.63.16,46.34.63.40,46.34.63.65,46.34.63.48,46.34.63.70,46.34.63.73,46.34.63.29,46.34.63.84,46.34.63.98,46.34.63.19,46.34.63.64,46.34.63.69,46.34.63.96,46.34.63.3,46.34.63.31,46.34.63.30,46.34.63.50,46.34.63.58,46.34.63.44,46.34.63.57,46.34.63.15,46.34.63.76,46.34.63.45,46.34.63.9,46.34.63.60,46.34.63.74,46.34.63.93,46.34.63.23,46.34.63.2,46.34.63.14,46.34.63.53,46.34.63.89,46.34.63.83,46.34.63.92,46.34.63.86,46.34.63.21,46.34.63.79,46.34.63.13,46.34.63.91,46.34.63.26,46.34.63.43,46.34.63.81,46.34.63.87</t>
-        </is>
-      </c>
-      <c r="Q25" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R25" s="20" t="inlineStr">
-        <is>
-          <t>已推送</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>172.17.215.206</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>210.232.81.231,90.179.77.207,54.92.173.232,1.1.1.1,171.176.77.133,36.190.172.72</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R25" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="n">
+        <v>46217.71452546296</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>incident-b9176288-e33b-44da-a40e-cfa01dc4275e</t>
+          <t>incident-8a7fb24f-cedb-4899-abeb-051fae193f82</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2931,27 +2928,27 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>172.16.156.68</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>疑似攻击行为</t>
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>主机失陷活动</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="G26" s="15" t="inlineStr">
-        <is>
-          <t>已忽略</t>
+          <t>银狐病毒</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -2970,39 +2967,39 @@
         </is>
       </c>
       <c r="K26" s="6" t="n">
-        <v>46217.43166666666</v>
+        <v>46213.04708333333</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>46217.43322916667</v>
+        <v>46213.04667824074</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>104.138.86.49</t>
+          <t>7.65.250.71</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>172.16.156.68</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="inlineStr">
-        <is>
-          <t>104.138.86.49</t>
-        </is>
-      </c>
-      <c r="Q26" s="5" t="inlineStr">
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
       </c>
-      <c r="R26" s="22" t="inlineStr">
-        <is>
-          <t>未推送</t>
+      <c r="R26" s="20" t="inlineStr">
+        <is>
+          <t>已推送</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -3014,7 +3011,7 @@
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>incident-2c914249-0e35-4895-8507-258167942379</t>
+          <t>incident-0a85403b-9a29-45d3-bf88-a63a30e3c411</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3024,17 +3021,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>172.24.82.56</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>10.143.166.101</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>病毒木马活动（病毒木马）</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
@@ -3042,9 +3039,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>处置完成</t>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -3063,32 +3060,32 @@
         </is>
       </c>
       <c r="K27" s="6" t="n">
-        <v>46217.43166666666</v>
+        <v>46216.71671296296</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>46217.43322916667</v>
+        <v>46216.71626157407</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>25.120.236.43</t>
+          <t>1.1.1.1</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>172.24.82.56</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr">
-        <is>
-          <t>25.120.236.43</t>
-        </is>
-      </c>
-      <c r="Q27" s="5" t="inlineStr">
+          <t>10.143.166.101</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>36.190.172.72,1.1.1.1,210.232.81.231,28.218.210.253,54.92.173.232,171.176.77.133</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -3098,16 +3095,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S27" s="6" t="n">
+        <v>46216.71804398148</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>incident-fe4c3af6-d61e-48a0-b265-345ddeb592d1</t>
+          <t>incident-e8610746-26a7-4c2c-9b9c-902a0df93a93</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3117,10 +3112,10 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>190.91.52.236</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
+          <t>172.24.16.15</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>真实攻击成功</t>
         </is>
@@ -3135,9 +3130,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -3156,32 +3151,32 @@
         </is>
       </c>
       <c r="K28" s="6" t="n">
-        <v>46217.43494212963</v>
+        <v>46216.48962962963</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>46217.43652777778</v>
+        <v>46216.48917824074</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>187.222.23.41</t>
+          <t>76.203.15.100</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>190.91.52.236</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="inlineStr">
-        <is>
-          <t>187.222.23.41</t>
-        </is>
-      </c>
-      <c r="Q28" s="5" t="inlineStr">
+          <t>172.24.16.15</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>76.203.15.100</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -3191,16 +3186,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S28" s="6" t="n">
+        <v>46216.4903125</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>incident-01cc335a-8308-4419-85cf-430f5dc3fc4c</t>
+          <t>incident-2ef66137-b5a1-42e1-8f27-ff09b3a83c2d</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3210,10 +3203,10 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>192.168.183.74</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
+          <t>10.142.159.118</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>疑似攻击行为</t>
         </is>
@@ -3249,32 +3242,32 @@
         </is>
       </c>
       <c r="K29" s="6" t="n">
-        <v>46217.41965277777</v>
+        <v>46217.74346064815</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>46217.42119212963</v>
+        <v>46217.74295138889</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>120.235.150.197</t>
+          <t>47.104.120.244</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>192.168.183.74</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t>120.235.150.197</t>
-        </is>
-      </c>
-      <c r="Q29" s="5" t="inlineStr">
+          <t>10.142.159.118</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>47.104.120.244</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -3284,16 +3277,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S29" s="6" t="n">
+        <v>46217.74612268519</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>incident-957b3f76-e41d-4fcb-84d2-99e78e71754e</t>
+          <t>incident-19e66a3c-0e5e-4746-8480-9e271bd19a72</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3303,17 +3294,17 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>172.30.122.166</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>10.98.137.220</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -3321,9 +3312,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>处置完成</t>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -3342,32 +3333,32 @@
         </is>
       </c>
       <c r="K30" s="6" t="n">
-        <v>46217.69356481481</v>
+        <v>46217.75984953704</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>46217.69516203704</v>
+        <v>46217.75938657407</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>69.213.137.251</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>172.30.122.166</t>
-        </is>
-      </c>
-      <c r="P30" s="5" t="inlineStr">
-        <is>
-          <t>24.246.113.51</t>
-        </is>
-      </c>
-      <c r="Q30" s="5" t="inlineStr">
+          <t>10.98.137.220</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>69.213.137.251</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -3377,16 +3368,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S30" s="6" t="n">
+        <v>46217.76135416667</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>incident-edd26b08-c6ce-4c46-8c5b-002b755b48ba</t>
+          <t>incident-cf97eaf4-4a22-4a74-9dee-ad5c15067e4d</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3396,17 +3385,17 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>172.20.207.251</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>192.168.79.123</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
@@ -3414,9 +3403,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -3435,32 +3424,32 @@
         </is>
       </c>
       <c r="K31" s="6" t="n">
-        <v>46217.42934027778</v>
+        <v>46216.73201388889</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>46217.43091435185</v>
+        <v>46216.73153935185</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>225.76.22.241</t>
+          <t>92.101.43.177</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>172.20.207.251</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q31" s="5" t="inlineStr">
+          <t>192.168.79.123</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>92.101.43.177</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -3470,16 +3459,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S31" s="6" t="n">
+        <v>46216.73342592592</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>incident-36ee5a69-33ec-46c6-89b7-641c15b2e15d</t>
+          <t>incident-bc8f7907-0962-41a3-b0eb-00018306a2c2</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3489,10 +3476,10 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>172.18.153.243</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
+          <t>10.103.23.102</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>疑似攻击行为</t>
         </is>
@@ -3528,32 +3515,32 @@
         </is>
       </c>
       <c r="K32" s="6" t="n">
-        <v>46217.44549768518</v>
+        <v>46216.70788194444</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>46217.44706018519</v>
+        <v>46216.7074074074</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>52.14.198.119</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>172.18.153.243</t>
-        </is>
-      </c>
-      <c r="P32" s="5" t="inlineStr">
-        <is>
-          <t>111.220.40.11</t>
-        </is>
-      </c>
-      <c r="Q32" s="5" t="inlineStr">
+          <t>10.103.23.102</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>52.14.198.119</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -3563,16 +3550,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S32" s="6" t="n">
+        <v>46216.71200231482</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>incident-7a1dddcc-6abb-44b7-a769-419366d08b4d</t>
+          <t>incident-d43ffce2-5469-4d00-aebb-ee1bbb4cbfdd</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3582,10 +3567,10 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>10.255.255.250</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
+          <t>172.17.3.133</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>疑似攻击行为</t>
         </is>
@@ -3621,32 +3606,32 @@
         </is>
       </c>
       <c r="K33" s="6" t="n">
-        <v>46217.45667824074</v>
+        <v>46216.70787037037</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>46217.45822916667</v>
+        <v>46216.7074074074</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>135.112.82.208</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10.255.255.250</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="inlineStr">
-        <is>
-          <t>210.232.81.231</t>
-        </is>
-      </c>
-      <c r="Q33" s="5" t="inlineStr">
+          <t>172.17.3.133</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>135.112.82.208</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -3656,16 +3641,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S33" s="6" t="n">
+        <v>46216.71207175926</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>incident-bda33275-20c1-4244-8232-a7ad2d5c71b0</t>
+          <t>incident-ff67742a-6451-46f0-ae27-528599fce5be</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3675,27 +3658,27 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>192.168.25.60</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
-        <is>
-          <t>已遏制</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -3714,32 +3697,32 @@
         </is>
       </c>
       <c r="K34" s="6" t="n">
-        <v>46216.64841435185</v>
+        <v>46216.73711805556</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>46217.46576388889</v>
+        <v>46216.73663194444</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>82.55.155.155</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q34" s="5" t="inlineStr">
+          <t>192.168.25.60</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>82.55.155.155</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -3749,16 +3732,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S34" s="6" t="n">
+        <v>46216.73825231481</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>incident-2a41cb55-56fe-4d80-bcac-88c309b4fa9e</t>
+          <t>incident-e501e766-799b-4431-ad9a-c6697dd7d324</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3768,27 +3749,27 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>132.179.222.47</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
-        <is>
-          <t>已遏制</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -3807,32 +3788,32 @@
         </is>
       </c>
       <c r="K35" s="6" t="n">
-        <v>46216.64356481482</v>
+        <v>46213.89177083333</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>46217.46575231481</v>
+        <v>46213.89136574074</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>55.255.65.225</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P35" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q35" s="5" t="inlineStr">
+          <t>132.179.222.47</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>55.255.65.225</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -3842,16 +3823,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S35" s="6" t="n">
+        <v>46213.89174768519</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>json.data.data[0].incidentRootIds.data[0]</t>
+          <t>incident-d4f7c67b-b2db-4bab-8a07-cf47c9b9564d</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3861,17 +3840,17 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>10.23.16.211</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>38.130.177.39</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
@@ -3879,9 +3858,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -3900,32 +3879,32 @@
         </is>
       </c>
       <c r="K36" s="6" t="n">
-        <v>46217.48283564814</v>
+        <v>46213.7940162037</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>46217.48438657408</v>
+        <v>46213.79362268518</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.1.1.1</t>
+          <t>145.191.83.169</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10.23.16.211</t>
-        </is>
-      </c>
-      <c r="P36" s="5" t="inlineStr">
-        <is>
-          <t>150.88.239.203</t>
-        </is>
-      </c>
-      <c r="Q36" s="5" t="inlineStr">
+          <t>38.130.177.39</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>145.191.83.169</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -3935,16 +3914,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S36" s="6" t="n">
+        <v>46213.79445601852</v>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>incident-a3cfe45e-0166-4b52-a75b-15b1cbf6f557</t>
+          <t>incident-c162bbf3-fda8-4740-8761-7db39961dca3</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3954,27 +3931,27 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>10.227.11.13</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>192.168.36.58</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G37" s="12" t="inlineStr">
-        <is>
-          <t>已遏制</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -3993,32 +3970,32 @@
         </is>
       </c>
       <c r="K37" s="6" t="n">
-        <v>46213.45025462963</v>
+        <v>46217.69126157407</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>46219.67665509259</v>
+        <v>46217.69076388889</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P37" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q37" s="5" t="inlineStr">
+          <t>192.168.36.58</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>99.103.99.92</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -4028,16 +4005,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S37" s="6" t="n">
+        <v>46217.6919212963</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>incident-3551db4b-2418-4da4-b647-eda411c01814</t>
+          <t>incident-a6e98366-7608-489c-914d-50871a03c3d8</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -4047,17 +4022,17 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>172.25.43.204</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>10.21.45.235</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
@@ -4065,9 +4040,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>处置完成</t>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -4086,32 +4061,32 @@
         </is>
       </c>
       <c r="K38" s="6" t="n">
-        <v>46217.4134837963</v>
+        <v>46217.69554398148</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>46217.41505787037</v>
+        <v>46217.6950462963</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.1.1.1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>172.25.43.204</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="inlineStr">
-        <is>
-          <t>54.92.173.232,165.132.204.41,210.232.81.231,1.1.1.1,171.176.77.133,36.190.172.72</t>
-        </is>
-      </c>
-      <c r="Q38" s="5" t="inlineStr">
+          <t>10.21.45.235</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>134.6.216.167</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -4121,16 +4096,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S38" s="6" t="n">
+        <v>46217.69778935185</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>incident-5ea3f105-bb69-48f7-b137-0235c88f8a7a</t>
+          <t>incident-5e1eff04-f36e-4b14-8ee7-d2cea5e7eac2</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4140,17 +4113,17 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>172.29.17.249</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>10.107.68.46</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>主机失陷活动（C2外联）</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
@@ -4158,9 +4131,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>处置完成</t>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -4179,14 +4152,14 @@
         </is>
       </c>
       <c r="K39" s="6" t="n">
-        <v>46217.413125</v>
+        <v>46217.71302083333</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>46217.41471064815</v>
+        <v>46217.71252314815</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -4196,15 +4169,15 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>172.29.17.249</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="inlineStr">
-        <is>
-          <t>autotest.com,36.190.172.72,231.92.189.161,test.example.com,sxfphishing.xyz,bnssyeoqps1234.com,1.1.1.1,210.232.81.231,qq-1319693778.cos.ap-nanjing.myqcloud.com,dcwrayvajwzzw.co,bb63fd178affccaab180bce1689157ce,59c3c2eba0192334a8fe82bdc07c8d6b,bnssyeoqps1232.com,bbnhh.icu,171.176.77.133,54.92.173.232</t>
-        </is>
-      </c>
-      <c r="Q39" s="5" t="inlineStr">
+          <t>10.107.68.46</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>210.232.81.231,bb63fd178affccaab180bce1689157ce,qq-1319693778.cos.ap-nanjing.myqcloud.com,test.example.com,sxfphishing.xyz,dcwrayvajwzzw.co,bnssyeoqps1232.com,bbnhh.icu,54.92.173.232,autotest.com,171.176.77.133,1.1.1.1,144.119.255.21,59c3c2eba0192334a8fe82bdc07c8d6b,bnssyeoqps1234.com,36.190.172.72</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -4214,16 +4187,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S39" s="6" t="n">
+        <v>46217.71678240741</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>incident-e4b11d5c-4cee-4b7f-81a8-469c02fad568</t>
+          <t>incident-6ff4a611-7ba0-456b-83c9-10dc672e7fe0</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -4233,10 +4204,10 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>192.168.184.232</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+          <t>141.62.33.88</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>疑似攻击行为</t>
         </is>
@@ -4272,32 +4243,32 @@
         </is>
       </c>
       <c r="K40" s="6" t="n">
-        <v>46217.43641203704</v>
+        <v>46217.59568287037</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>46217.43797453704</v>
+        <v>46217.59521990741</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>114.215.223.231</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>192.168.184.232</t>
-        </is>
-      </c>
-      <c r="P40" s="5" t="inlineStr">
-        <is>
-          <t>122.87.255.104</t>
-        </is>
-      </c>
-      <c r="Q40" s="5" t="inlineStr">
+          <t>141.62.33.88</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>114.215.223.231</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -4307,16 +4278,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S40" s="6" t="n">
+        <v>46217.59928240741</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>incident-aaf179a8-0e4d-4950-8555-81865a489d5c</t>
+          <t>incident-8e0b2ade-9faf-4ad4-8410-8f90ef2fb666</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -4326,17 +4295,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>192.168.127.27</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>192.168.23.169</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
@@ -4344,9 +4313,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G41" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="G41" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -4365,32 +4334,32 @@
         </is>
       </c>
       <c r="K41" s="6" t="n">
-        <v>46217.43414351852</v>
+        <v>46216.63510416666</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>46217.43571759259</v>
+        <v>46216.63466435186</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>166.225.81.35</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P41" s="5" t="inlineStr">
-        <is>
-          <t>210.115.26.174</t>
-        </is>
-      </c>
-      <c r="Q41" s="5" t="inlineStr">
+          <t>192.168.23.169</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>166.225.81.35</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -4400,16 +4369,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S41" s="6" t="n">
+        <v>46216.63510416666</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>incident-c4cd2c18-5cff-4edc-a0e0-9f315071d523</t>
+          <t>incident-d6aef2d5-83d6-4d8a-9219-50138fee0d19</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -4419,27 +4386,27 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>主机失陷活动</t>
+          <t>172.19.10.60</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>勒索攻击</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>处置完成</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -4458,81 +4425,79 @@
         </is>
       </c>
       <c r="K42" s="6" t="n">
-        <v>46216.64841435185</v>
+        <v>46217.75707175926</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>46216.8025462963</v>
+        <v>46217.7566087963</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P42" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q42" s="5" t="inlineStr">
+          <t>172.19.10.60</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>153.165.74.10</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
       </c>
-      <c r="R42" s="20" t="inlineStr">
-        <is>
-          <t>已推送</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R42" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="n">
+        <v>46217.75796296296</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>incident-edee761e-259b-4207-ae11-d68596b51630</t>
+          <t>incident-6ec5ca43-9dc9-45e5-8c6c-78cfbb7e4fcd</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+          <t>主机存在通过命令窃取Lsa凭证</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>主机失陷活动</t>
+          <t>10.223.2.62</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>勒索攻击</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>处置完成</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -4542,60 +4507,58 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>WebShell管理工具</t>
-        </is>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>成功</t>
+          <t>窃密工具</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>尝试</t>
         </is>
       </c>
       <c r="K43" s="6" t="n">
-        <v>46216.80203703704</v>
+        <v>46214.78564814815</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>46216.8025462963</v>
+        <v>46213.79275462963</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P43" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q43" s="5" t="inlineStr">
-        <is>
-          <t>STA (86A45542)</t>
-        </is>
-      </c>
-      <c r="R43" s="20" t="inlineStr">
-        <is>
-          <t>已推送</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>1424b0737f0c9778400d69417efd6a21</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>EDR (aES_wmt_cloud_key_02-30136054337)</t>
+        </is>
+      </c>
+      <c r="R43" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="n">
+        <v>46216.68130787037</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>incident-2a41cb55-56fe-4d80-bcac-88c309b4fa9q</t>
+          <t>incident-b3173bae-fc10-40d2-b96a-0701a911530f</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -4605,27 +4568,27 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>主机失陷活动</t>
+          <t>11.11.11.11</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>勒索攻击</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>处置完成</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>待处置</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -4644,39 +4607,39 @@
         </is>
       </c>
       <c r="K44" s="6" t="n">
-        <v>46216.64356481482</v>
+        <v>46213.42516203703</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>46216.8025462963</v>
+        <v>46213.4247337963</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>11.11.12.2</t>
+          <t>33.94.99.144</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>192.168.50.2</t>
-        </is>
-      </c>
-      <c r="P44" s="5" t="inlineStr">
-        <is>
-          <t>11.11.12.2</t>
-        </is>
-      </c>
-      <c r="Q44" s="5" t="inlineStr">
+          <t>11.11.11.11</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>33.94.99.144</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
       </c>
-      <c r="R44" s="20" t="inlineStr">
-        <is>
-          <t>已推送</t>
+      <c r="R44" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -4688,7 +4651,7 @@
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>incident-2ebeead2-5c5a-4aef-a2fc-1e90e289a39e</t>
+          <t>incident-5e770e85-76b9-4182-a407-cf67043f99c7</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -4698,17 +4661,17 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>10.94.204.92</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>192.168.4.109</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
@@ -4716,9 +4679,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -4737,32 +4700,32 @@
         </is>
       </c>
       <c r="K45" s="6" t="n">
-        <v>46217.42388888889</v>
+        <v>46217.74846064814</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>46217.42547453703</v>
+        <v>46217.74798611111</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>211.69.33.96</t>
+          <t>113.43.168.84</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>10.94.204.92</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="inlineStr">
-        <is>
-          <t>211.69.33.96</t>
-        </is>
-      </c>
-      <c r="Q45" s="5" t="inlineStr">
+          <t>192.168.4.109</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>113.43.168.84</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -4772,16 +4735,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S45" s="6" t="n">
+        <v>46217.74945601852</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>incident-ff14450f-26cd-45b4-8631-24c4300d0959</t>
+          <t>incident-645d2250-123e-46a7-be8d-4d2a2797c888</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -4791,17 +4752,17 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>10.137.167.43</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>192.168.70.20</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
@@ -4809,9 +4770,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G46" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -4830,32 +4791,32 @@
         </is>
       </c>
       <c r="K46" s="6" t="n">
-        <v>46217.439375</v>
+        <v>46216.71057870371</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>46217.44092592593</v>
+        <v>46216.71012731481</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>164.180.76.152</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>10.137.167.43</t>
-        </is>
-      </c>
-      <c r="P46" s="5" t="inlineStr">
-        <is>
-          <t>3.209.163.193</t>
-        </is>
-      </c>
-      <c r="Q46" s="5" t="inlineStr">
+          <t>192.168.70.20</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>164.180.76.152</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -4865,16 +4826,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S46" s="6" t="n">
+        <v>46216.71408564815</v>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>incident-9eccfcef-411a-4093-b757-0b64309c14ce</t>
+          <t>incident-b41acef9-b59e-40d0-97a6-10af3abde277</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4884,17 +4843,17 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>10.214.67.218</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>疑似攻击行为</t>
+          <t>172.26.224.91</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>真实攻击成功</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>银狐病毒</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
@@ -4902,9 +4861,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>已忽略</t>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -4923,32 +4882,32 @@
         </is>
       </c>
       <c r="K47" s="6" t="n">
-        <v>46217.47622685185</v>
+        <v>46216.49103009259</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>46217.47778935185</v>
+        <v>46216.49056712963</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>30.227.242.252</t>
+          <t>53.23.95.107</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>10.214.67.218</t>
-        </is>
-      </c>
-      <c r="P47" s="5" t="inlineStr">
-        <is>
-          <t>30.227.242.252</t>
-        </is>
-      </c>
-      <c r="Q47" s="5" t="inlineStr">
+          <t>172.26.224.91</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>53.23.95.107</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -4958,16 +4917,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S47" s="6" t="n">
+        <v>46216.49170138889</v>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>incident-57a01ca7-0be5-46e4-b9ef-77da8d87c2e0</t>
+          <t>incident-4ad19a94-3669-4926-a397-6eaaac9a09ae</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -4977,17 +4934,17 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>10.95.118.135</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>10.60.229.235</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
@@ -4995,9 +4952,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G48" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -5016,32 +4973,32 @@
         </is>
       </c>
       <c r="K48" s="6" t="n">
-        <v>46217.45089120371</v>
+        <v>46216.63893518518</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>46217.45244212963</v>
+        <v>46216.6384837963</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>92.92.121.178</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>10.95.118.135</t>
-        </is>
-      </c>
-      <c r="P48" s="5" t="inlineStr">
-        <is>
-          <t>69.181.97.1</t>
-        </is>
-      </c>
-      <c r="Q48" s="5" t="inlineStr">
+          <t>10.60.229.235</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>92.92.121.178</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -5051,16 +5008,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S48" s="6" t="n">
+        <v>46216.63934027778</v>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>incident-2bfd5f9b-6850-4d4c-abd5-c812f738ff78</t>
+          <t>incident-d6525918-00ec-42ec-bf4a-b57631c17647</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -5070,10 +5025,10 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>192.168.11.195</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
+          <t>192.168.199.179</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>疑似攻击行为</t>
         </is>
@@ -5109,32 +5064,32 @@
         </is>
       </c>
       <c r="K49" s="6" t="n">
-        <v>46217.43672453704</v>
+        <v>46216.63033564815</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>46217.43826388889</v>
+        <v>46216.62986111111</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>215.139.13.17</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>192.168.11.195</t>
-        </is>
-      </c>
-      <c r="P49" s="5" t="inlineStr">
-        <is>
-          <t>55.173.56.248</t>
-        </is>
-      </c>
-      <c r="Q49" s="5" t="inlineStr">
+          <t>192.168.199.179</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>215.139.13.17</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -5144,16 +5099,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S49" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S49" s="6" t="n">
+        <v>46216.63072916667</v>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>incident-e42129f5-2b15-409d-9504-af7791f2bd92</t>
+          <t>incident-5d5d9edf-a180-491a-adc6-8dc9d09c3ed9</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -5163,17 +5116,17 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>10.191.22.229</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>疑似攻击行为</t>
+          <t>10.45.155.159</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>真实攻击成功</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>银狐病毒</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
@@ -5181,9 +5134,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G50" s="15" t="inlineStr">
-        <is>
-          <t>已忽略</t>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -5202,32 +5155,32 @@
         </is>
       </c>
       <c r="K50" s="6" t="n">
-        <v>46217.43493055556</v>
+        <v>46216.70828703704</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>46217.43652777778</v>
+        <v>46216.7078125</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>214.47.248.46</t>
+          <t>117.3.47.165</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>10.191.22.229</t>
-        </is>
-      </c>
-      <c r="P50" s="5" t="inlineStr">
-        <is>
-          <t>214.47.248.46</t>
-        </is>
-      </c>
-      <c r="Q50" s="5" t="inlineStr">
+          <t>10.45.155.159</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>117.3.47.165</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -5237,16 +5190,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S50" s="6" t="n">
+        <v>46216.7078587963</v>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>incident-2c90c655-d691-4740-a351-c4706abe4995</t>
+          <t>incident-80e113dc-7e46-4603-ad83-3e5c2f476cb8</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -5256,10 +5207,10 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>172.21.117.213</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
+          <t>10.6.88.232</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>疑似攻击行为</t>
         </is>
@@ -5295,32 +5246,32 @@
         </is>
       </c>
       <c r="K51" s="6" t="n">
-        <v>46217.44197916667</v>
+        <v>46216.6327662037</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>46217.44353009259</v>
+        <v>46216.63229166667</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>114.9.149.161</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>172.21.117.213</t>
-        </is>
-      </c>
-      <c r="P51" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q51" s="5" t="inlineStr">
+          <t>10.6.88.232</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>114.9.149.161</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -5330,16 +5281,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S51" s="6" t="n">
+        <v>46216.63309027778</v>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>incident-c3f25d82-ce83-4b25-af75-4a4a68c81e78</t>
+          <t>incident-7e7ea1fd-e02f-4ef2-9069-33c9aadd09b4</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -5349,17 +5298,17 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>192.168.74.228</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>192.168.101.37</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
@@ -5367,9 +5316,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -5388,32 +5337,32 @@
         </is>
       </c>
       <c r="K52" s="6" t="n">
-        <v>46217.42788194444</v>
+        <v>46217.74208333333</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>46217.42946759259</v>
+        <v>46217.74162037037</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>226.245.70.192</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>192.168.74.228</t>
-        </is>
-      </c>
-      <c r="P52" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q52" s="5" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>179.88.218.61</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -5423,16 +5372,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S52" s="6" t="n">
+        <v>46217.74521990741</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>incident-9b5196e9-67c6-4dfd-b5d0-219eced024e6</t>
+          <t>incident-09ee4b26-6622-41b8-b0d4-f3c3abcc0712</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -5442,17 +5389,17 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>10.232.136.178</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>疑似攻击行为</t>
+          <t>192.168.143.44</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>病毒木马活动（病毒木马）</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>银狐病毒</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
@@ -5460,9 +5407,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G53" s="15" t="inlineStr">
-        <is>
-          <t>已忽略</t>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -5481,32 +5428,32 @@
         </is>
       </c>
       <c r="K53" s="6" t="n">
-        <v>46217.44537037037</v>
+        <v>46216.49710648148</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>46217.44694444445</v>
+        <v>46216.49664351852</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.1.1.1</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>10.232.136.178</t>
-        </is>
-      </c>
-      <c r="P53" s="5" t="inlineStr">
-        <is>
-          <t>189.151.154.33</t>
-        </is>
-      </c>
-      <c r="Q53" s="5" t="inlineStr">
+          <t>192.168.143.44</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>171.176.77.133,36.190.172.72,54.92.173.232,1.1.1.1,38.78.90.209,210.232.81.231</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -5516,16 +5463,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S53" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S53" s="6" t="n">
+        <v>46216.49725694444</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>incident-e4008561-0880-4bd6-8acc-84b6363bbadb</t>
+          <t>incident-6bd605af-9080-4fe4-84b7-1213b11fd238</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -5535,17 +5480,17 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>10.49.244.43</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>真实攻击成功</t>
+          <t>172.20.140.212</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
@@ -5553,9 +5498,9 @@
           <t>中危</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
+      <c r="G54" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -5574,32 +5519,32 @@
         </is>
       </c>
       <c r="K54" s="6" t="n">
-        <v>46217.41964120371</v>
+        <v>46216.62267361111</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>46217.42119212963</v>
+        <v>46216.62222222222</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>测试001</t>
+          <t>中国华能集团有限公司福建分公司</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>48.77.249.29</t>
+          <t>72.206.250.92</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>10.49.244.43</t>
-        </is>
-      </c>
-      <c r="P54" s="5" t="inlineStr">
-        <is>
-          <t>48.77.249.29</t>
-        </is>
-      </c>
-      <c r="Q54" s="5" t="inlineStr">
+          <t>172.20.140.212</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>72.206.250.92</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
@@ -5609,16 +5554,14 @@
           <t>未推送</t>
         </is>
       </c>
-      <c r="S54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S54" s="6" t="n">
+        <v>46216.62267361111</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>incident-a262251c-b191-462e-a525-8ea83b1df3a0</t>
+          <t>incident-0692a3d8-5b7f-4fe4-8dc9-4bc5fbe356ee</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -5628,84 +5571,2909 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>172.23.156.58</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
+          <t>192.168.183.236</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>46216.71707175926</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>46216.7166087963</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>53.53.22.58</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>192.168.183.236</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>53.53.22.58</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R55" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S55" s="6" t="n">
+        <v>46216.71804398148</v>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>incident-01787ae8-c6db-446e-bf76-6e3aef160316</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>192.168.87.147</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>46216.73738425926</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>46216.73692129629</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>168.45.166.179</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R56" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S56" s="6" t="n">
+        <v>46216.73825231481</v>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>incident-ba486449-edf3-4fde-90cf-2f355c188e44</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>10.251.93.250</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>46216.62668981482</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>46216.62621527778</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>102.56.93.130</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>10.251.93.250</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>102.56.93.130</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R57" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S57" s="6" t="n">
+        <v>46216.62701388889</v>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>incident-20d9f00b-5386-4de6-9467-810380278582</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>172.19.29.169</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G58" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>46216.63071759259</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>46216.63026620371</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>208.30.247.238</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>172.19.29.169</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>208.30.247.238</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R58" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S58" s="6" t="n">
+        <v>46216.63104166667</v>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>incident-cc034950-4086-4255-bc93-f07e4d6a513b</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>192.168.99.218</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G59" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>46217.74186342592</v>
+      </c>
+      <c r="L59" s="6" t="n">
+        <v>46217.74138888889</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>192.168.99.218</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>196.224.196.109</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R59" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S59" s="6" t="n">
+        <v>46217.74372685186</v>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>incident-7571e6a7-4705-4153-9ceb-b790a63fb214</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>252.51.59.117</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G60" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>46216.66017361111</v>
+      </c>
+      <c r="L60" s="6" t="n">
+        <v>46216.65972222222</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>190.68.42.34</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>252.51.59.117</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>190.68.42.34</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R60" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S60" s="6" t="n">
+        <v>46216.66052083333</v>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>incident-d926cbb8-5912-487f-8ef1-8342646943bb</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>215.9.206.180</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>待处置</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>46213.0453587963</v>
+      </c>
+      <c r="L61" s="6" t="n">
+        <v>46213.04494212963</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>63.186.42.17</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>215.9.206.180</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>63.186.42.17</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R61" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>incident-05ef0493-181a-4c4b-9848-17eb56c658d1</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>210.26.94.181</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G62" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="n">
+        <v>46216.48769675926</v>
+      </c>
+      <c r="L62" s="6" t="n">
+        <v>46216.48721064815</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>175.159.228.123</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>210.26.94.181</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>175.159.228.123</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R62" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S62" s="6" t="n">
+        <v>46216.48802083333</v>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>incident-a18365ca-8960-4ba9-8a32-3316a31dd351</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>143.34.163.182</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G63" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>46216.78228009259</v>
+      </c>
+      <c r="L63" s="6" t="n">
+        <v>46216.7818287037</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>183.55.24.214</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>143.34.163.182</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>183.55.24.214</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R63" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S63" s="6" t="n">
+        <v>46216.78866898148</v>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>incident-a94a4496-b11d-46e9-91a8-d8c49801f0d2</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>226.136.92.156</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G64" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="n">
+        <v>46216.70788194444</v>
+      </c>
+      <c r="L64" s="6" t="n">
+        <v>46216.7074074074</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>162.119.85.254</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>226.136.92.156</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>162.119.85.254</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R64" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S64" s="6" t="n">
+        <v>46216.71207175926</v>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>incident-6fc4e46c-6b25-4372-9f6a-71e7e22da85e</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>192.168.137.150</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="n">
+        <v>46217.75930555556</v>
+      </c>
+      <c r="L65" s="6" t="n">
+        <v>46217.75880787037</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>176.165.127.39</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R65" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S65" s="6" t="n">
+        <v>46217.76053240741</v>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>incident-c5dc25fb-b489-4ab2-8a53-dcaa2086da65</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>162.95.107.148</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G66" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="n">
+        <v>46217.42275462963</v>
+      </c>
+      <c r="L66" s="6" t="n">
+        <v>46217.42224537037</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>20.224.228.160</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>162.95.107.148</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>20.224.228.160</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R66" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S66" s="6" t="n">
+        <v>46217.42358796296</v>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>incident-71c560f2-d13f-42d6-af6f-568e8868a995</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>172.21.81.5</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G67" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="n">
+        <v>46217.71372685185</v>
+      </c>
+      <c r="L67" s="6" t="n">
+        <v>46217.71327546296</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>137.111.244.227</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>172.21.81.5</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>137.111.244.227</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R67" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S67" s="6" t="n">
+        <v>46217.7145949074</v>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>incident-15de5c2b-390c-44b2-bb84-d16a352f9843</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>172.22.74.193</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>主机失陷活动（C2外联）</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G68" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="n">
+        <v>46217.74275462963</v>
+      </c>
+      <c r="L68" s="6" t="n">
+        <v>46217.74225694445</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>172.22.74.193</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>dcwrayvajwzzw.co,bbnhh.icu,bnssyeoqps1234.com,234.37.138.166,autotest.com,59c3c2eba0192334a8fe82bdc07c8d6b,test.example.com,171.176.77.133,54.92.173.232,bb63fd178affccaab180bce1689157ce,qq-1319693778.cos.ap-nanjing.myqcloud.com,1.1.1.1,bnssyeoqps1232.com,sxfphishing.xyz,210.232.81.231,36.190.172.72</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R68" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="n">
+        <v>46217.74403935186</v>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>incident-eb1b77b9-2f7f-46ec-a1ac-13a5a9c63503</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>主机存在通过命令窃取Lsa凭证</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>10.223.2.62</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>窃密工具</t>
+        </is>
+      </c>
+      <c r="J69" s="19" t="inlineStr">
+        <is>
+          <t>尝试</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="n">
+        <v>46216.63913194444</v>
+      </c>
+      <c r="L69" s="6" t="n">
+        <v>46211.69542824074</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>1424b0737f0c9778400d69417efd6a21</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>EDR (aES_wmt_cloud_key_02-30136054337)</t>
+        </is>
+      </c>
+      <c r="R69" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S69" s="6" t="n">
+        <v>46220.72321759259</v>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>incident-1aff9536-d668-444a-85ab-80adef7c55f6</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>病毒木马活动（病毒木马）</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>银狐病毒</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="n">
+        <v>46216.62841435185</v>
+      </c>
+      <c r="L70" s="6" t="n">
+        <v>46216.62795138889</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>31.72.84.195</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>210.232.81.231</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R70" s="20" t="inlineStr">
+        <is>
+          <t>已推送</t>
+        </is>
+      </c>
+      <c r="S70" s="6" t="n">
+        <v>46223.7015625</v>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>incident-0242da27-056f-44fa-ada8-467fdb9c097d</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>172.25.203.7</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G71" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="n">
+        <v>46216.62240740741</v>
+      </c>
+      <c r="L71" s="6" t="n">
+        <v>46216.62193287037</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>164.214.105.245</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>172.25.203.7</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>164.214.105.245</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R71" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S71" s="6" t="n">
+        <v>46216.62339120371</v>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>incident-6fe35541-9a19-4b93-a673-a90fd9a9536d</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>11.11.11.11</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="n">
+        <v>46213.42329861111</v>
+      </c>
+      <c r="L72" s="6" t="n">
+        <v>46213.42288194445</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>127.252.213.206</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>11.11.11.11</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R72" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>incident-fc2f22a8-84ee-4116-961b-5d43ca1383f4</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>11.11.11.11</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="n">
+        <v>46213.78582175926</v>
+      </c>
+      <c r="L73" s="6" t="n">
+        <v>46213.7854050926</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>194.101.133.142</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>11.11.11.11</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>194.101.133.142</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R73" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S73" s="6" t="n">
+        <v>46213.78737268518</v>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>incident-5f1a9779-48cd-444d-acec-d8920b2dccf2</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>11.11.11.11</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>已遏制</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>46213.50234953704</v>
+      </c>
+      <c r="L74" s="6" t="n">
+        <v>46213.50193287037</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>247.90.69.16</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>11.11.11.11</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R74" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>incident-1b667909-4c5b-4277-b6df-d3dd2da86b69</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>192.168.12.18</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G75" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="n">
+        <v>46216.64104166667</v>
+      </c>
+      <c r="L75" s="6" t="n">
+        <v>46216.64056712963</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>181.161.61.151</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>192.168.12.18</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>181.161.61.151</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R75" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S75" s="6" t="n">
+        <v>46216.64189814815</v>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>incident-4fc496a6-1d06-4bc9-8948-0aa7773366f0</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>172.28.218.90</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>真实攻击成功</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>银狐病毒</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F76" s="9" t="inlineStr">
         <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr">
-        <is>
-          <t>待处置</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>后门攻击事件</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>WebShell管理工具</t>
         </is>
       </c>
-      <c r="J55" s="16" t="inlineStr">
+      <c r="J76" s="16" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="K55" s="6" t="n">
-        <v>46217.41383101852</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>46217.41540509259</v>
-      </c>
-      <c r="M55" s="3" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="N55" s="3" t="inlineStr">
-        <is>
-          <t>26.50.118.200</t>
-        </is>
-      </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>172.23.156.58</t>
-        </is>
-      </c>
-      <c r="P55" s="5" t="inlineStr">
-        <is>
-          <t>26.50.118.200</t>
-        </is>
-      </c>
-      <c r="Q55" s="5" t="inlineStr">
+      <c r="K76" s="6" t="n">
+        <v>46216.59443287037</v>
+      </c>
+      <c r="L76" s="6" t="n">
+        <v>46216.59398148148</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>105.88.9.239</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>172.28.218.90</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>105.88.9.239</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="inlineStr">
         <is>
           <t>STA (86A45542)</t>
         </is>
       </c>
-      <c r="R55" s="22" t="inlineStr">
+      <c r="R76" s="22" t="inlineStr">
         <is>
           <t>未推送</t>
         </is>
       </c>
-      <c r="S55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S76" s="6" t="n">
+        <v>46216.59517361111</v>
+      </c>
+    </row>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>incident-dc6fb333-0343-418f-904d-b19689daff21</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>172.20.114.36</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>主机失陷活动</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J77" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="n">
+        <v>46216.71636574074</v>
+      </c>
+      <c r="L77" s="6" t="n">
+        <v>46216.71591435185</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>172.20.114.36</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>bb63fd178affccaab180bce1689157ce,test.example.com,1.1.1.1,171.176.77.133,67.150.84.137,qq-1319693778.cos.ap-nanjing.myqcloud.com,bbnhh.icu,sxfphishing.xyz,bnssyeoqps1234.com,bnssyeoqps1232.com,dcwrayvajwzzw.co,59c3c2eba0192334a8fe82bdc07c8d6b,autotest.com,210.232.81.231,36.190.172.72,54.92.173.232</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R77" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S77" s="6" t="n">
+        <v>46216.71635416667</v>
+      </c>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>incident-f204c870-b84f-41ec-9c2e-d897ef40a30f</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>172.19.140.129</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J78" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="n">
+        <v>46216.70918981481</v>
+      </c>
+      <c r="L78" s="6" t="n">
+        <v>46216.70873842593</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>97.101.18.156</t>
+        </is>
+      </c>
+      <c r="Q78" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R78" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S78" s="6" t="n">
+        <v>46216.71572916667</v>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>incident-3e57a945-0535-45f4-ab6b-5e6dbf15a771</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>10.212.42.87</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>46216.71087962963</v>
+      </c>
+      <c r="L79" s="6" t="n">
+        <v>46216.71041666667</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>218.242.242.126</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>10.212.42.87</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>218.242.242.126</t>
+        </is>
+      </c>
+      <c r="Q79" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R79" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S79" s="6" t="n">
+        <v>46216.71425925926</v>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>incident-93cd9f38-7a7a-49c9-af27-e91a7467dfb4</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>10.212.199.138</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J80" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="n">
+        <v>46217.77584490741</v>
+      </c>
+      <c r="L80" s="6" t="n">
+        <v>46217.77535879629</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>209.161.21.69</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>10.212.199.138</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>209.161.21.69</t>
+        </is>
+      </c>
+      <c r="Q80" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R80" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S80" s="6" t="n">
+        <v>46217.77667824074</v>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>incident-dfa9fabe-e4d7-4e5b-a688-fe815b06fd09</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>172.24.49.81</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>病毒木马活动（病毒木马）</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>银狐病毒</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J81" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>46216.49675925926</v>
+      </c>
+      <c r="L81" s="6" t="n">
+        <v>46216.4962962963</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
+          <t>172.24.49.81</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>210.232.81.231,dcwrayvajwzzw.co,test.example.com,sxfphishing.xyz,43.165.229.167,qq-1319693778.cos.ap-nanjing.myqcloud.com,autotest.com,bnssyeoqps1232.com,bnssyeoqps1234.com,bbnhh.icu,171.176.77.133,54.92.173.232,1.1.1.1,bb63fd178affccaab180bce1689157ce,59c3c2eba0192334a8fe82bdc07c8d6b,36.190.172.72</t>
+        </is>
+      </c>
+      <c r="Q81" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R81" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="n">
+        <v>46216.49725694444</v>
+      </c>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>incident-20cbef61-0e00-42bd-814e-8727d5c1cd8a</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>192.168.196.77</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G82" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J82" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>46217.75950231482</v>
+      </c>
+      <c r="L82" s="6" t="n">
+        <v>46217.75903935185</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="inlineStr">
+        <is>
+          <t>192.168.196.77</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>171.176.77.133,210.232.81.231,36.190.172.72,54.92.173.232,1.1.1.1,138.112.51.80</t>
+        </is>
+      </c>
+      <c r="Q82" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R82" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S82" s="6" t="n">
+        <v>46217.76039351852</v>
+      </c>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>incident-ea22fe90-4605-4a1d-a560-064fe1729614</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>172.21.80.40</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>病毒木马活动（病毒木马）</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G83" s="15" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J83" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>46217.75914351852</v>
+      </c>
+      <c r="L83" s="6" t="n">
+        <v>46217.75863425926</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>172.21.80.40</t>
+        </is>
+      </c>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1,autotest.com,qq-1319693778.cos.ap-nanjing.myqcloud.com,bb63fd178affccaab180bce1689157ce,171.176.77.133,bnssyeoqps1232.com,sxfphishing.xyz,54.92.173.232,36.190.172.72,210.232.81.231,dcwrayvajwzzw.co,bnssyeoqps1234.com,237.70.17.14,59c3c2eba0192334a8fe82bdc07c8d6b,test.example.com,bbnhh.icu</t>
+        </is>
+      </c>
+      <c r="Q83" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R83" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S83" s="6" t="n">
+        <v>46217.76084490741</v>
+      </c>
+    </row>
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>incident-b3d125b1-0ce4-413f-bca0-c88438675023</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>真实攻击成功</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>银狐病毒</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J84" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>46216.49407407407</v>
+      </c>
+      <c r="L84" s="6" t="n">
+        <v>46216.49363425926</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>40.115.235.166</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>210.232.81.231</t>
+        </is>
+      </c>
+      <c r="Q84" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R84" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S84" s="6" t="n">
+        <v>46216.49396990741</v>
+      </c>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>incident-da2b2ecb-df1d-4ccf-a473-0da2918001fd</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>疑似攻击行为</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J85" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>46216.62216435185</v>
+      </c>
+      <c r="L85" s="6" t="n">
+        <v>46216.62170138889</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
+          <t>100.48.38.127</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
+          <t>1.1.1.1</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>210.232.81.231</t>
+        </is>
+      </c>
+      <c r="Q85" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R85" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S85" s="6" t="n">
+        <v>46216.62295138889</v>
+      </c>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>incident-8869e0c9-b0bc-4551-9482-c289dff80970</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>主机存在Chopper 2014版PHP Webshell上传</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>真实攻击成功</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>银狐病毒</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>处置完成</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>后门攻击事件</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>WebShell管理工具</t>
+        </is>
+      </c>
+      <c r="J86" s="16" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>46216.49424768519</v>
+      </c>
+      <c r="L86" s="6" t="n">
+        <v>46216.49380787037</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>中国华能集团有限公司福建分公司</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>177.79.216.103</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="inlineStr">
+        <is>
+          <t>114.114.114.114</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>210.232.81.231</t>
+        </is>
+      </c>
+      <c r="Q86" s="3" t="inlineStr">
+        <is>
+          <t>STA (86A45542)</t>
+        </is>
+      </c>
+      <c r="R86" s="22" t="inlineStr">
+        <is>
+          <t>未推送</t>
+        </is>
+      </c>
+      <c r="S86" s="6" t="n">
+        <v>46216.49396990741</v>
       </c>
     </row>
   </sheetData>

--- a/安全体检报告/风险清单/安全事件清单.xlsx
+++ b/安全体检报告/风险清单/安全事件清单.xlsx
@@ -691,7 +691,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -719,6 +719,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1278,10 +1281,10 @@
           <t>成功</t>
         </is>
       </c>
-      <c r="K2" s="10" t="n">
+      <c r="K2" s="11" t="n">
         <v>46213.04708333333</v>
       </c>
-      <c r="L2" s="10" t="n">
+      <c r="L2" s="11" t="n">
         <v>46213.88939814815</v>
       </c>
       <c r="M2" s="8" t="inlineStr">
@@ -1314,10 +1317,8 @@
           <t>已推送</t>
         </is>
       </c>
-      <c r="S2" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S2" s="10" t="n">
+        <v>46223.04708333333</v>
       </c>
     </row>
   </sheetData>
